--- a/2022 data/excel_outputs/124_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/124_boothwise_data.xlsx
@@ -14,9 +14,81 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="87">
   <si>
     <t>AC 124 Booth-wise Data</t>
+  </si>
+  <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
   </si>
   <si>
     <t>BOOTH ID</t>
@@ -25,412 +97,115 @@
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>###### ##### #0##0##0 ##### #### ### ###### #0##0#</t>
+    <t>NAN</t>
   </si>
   <si>
-    <t>###### ##### #0##0##0 ##### #### ### ###### #0##0 #</t>
+    <t>KAMRA NO. 9 WUDRO SINIYAR SECENDRY SCHOOL RAJENDRA NAGAR</t>
   </si>
   <si>
-    <t>###### ##### #0##0##0 ##### #### ### ###### #0##0 6</t>
+    <t>NAN ROOM NO. 407</t>
   </si>
   <si>
-    <t>######## ##### ###### #0 ##0 #</t>
+    <t>NAN ROOM ROOM NO. 408</t>
   </si>
   <si>
-    <t>######## ##### ###### #0##0 #</t>
+    <t>NAN ROOM ROOM ROOM NO. 409</t>
   </si>
   <si>
-    <t>######## ##### ####### #0 ##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM NO. 410</t>
   </si>
   <si>
-    <t>######## ##### ##### ####### ###### #0##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM NO. 411</t>
   </si>
   <si>
-    <t>####### ### ###### ###### ##### ####### ####### ###### #0##0#</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM NO. 412</t>
   </si>
   <si>
-    <t>####### ### ###### ###### ##### ####### ####### ###### #0##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 413</t>
   </si>
   <si>
-    <t>######## ##### ##### ####### ####### #0##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 414</t>
   </si>
   <si>
-    <t>######## ######### ##### ####### #0##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 415</t>
   </si>
   <si>
-    <t>####### ### ###### ###### ##### ####### ####### ####### #0##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 416</t>
   </si>
   <si>
-    <t>##### ######### ###### ######## #0##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 417</t>
   </si>
   <si>
-    <t>####### ##### ##### ##### ###### #0##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 418</t>
   </si>
   <si>
-    <t>##### #### ######## ####### ###### ####### #0 ##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 419</t>
   </si>
   <si>
-    <t>#### ######## ##### ######## #0 ##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 420</t>
   </si>
   <si>
-    <t>##### #### ###### ### ##### ######## #0 ##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 421</t>
   </si>
   <si>
-    <t>######## ####### ##### ####### #0##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 422</t>
   </si>
   <si>
-    <t>####### ###### ##### ##### ###### ###### #0##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 423</t>
   </si>
   <si>
-    <t>##### ####### ##### ##### #0 ##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 424</t>
   </si>
   <si>
-    <t>####### ###### ##### ###### ###### #0 ##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 425</t>
   </si>
   <si>
-    <t>###### ###### ### ##### ########## #0##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 426</t>
   </si>
   <si>
-    <t>##### ####### ###### ### ##### ##### #0##0#</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 427</t>
   </si>
   <si>
-    <t>##### ####### ###### ### ##### ##### #0##0 5</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 428</t>
   </si>
   <si>
-    <t>##### ####### ###### ### ##### ##### #0##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 429</t>
   </si>
   <si>
-    <t>#### ##### ##### #### ###### #0 ##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 430</t>
   </si>
   <si>
-    <t>### #### ######## ### #### ########## #0##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 431</t>
   </si>
   <si>
-    <t>### #### ######## ### #### ########## ### ### ######</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 432</t>
   </si>
   <si>
-    <t>### #### ######## ### #### ########## ### ### #######</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 433</t>
   </si>
   <si>
-    <t>######## ####### ###### ####### #0##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 434</t>
   </si>
   <si>
-    <t>###### ##### ##### ####### ###### #0 ##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 435</t>
   </si>
   <si>
-    <t>### ####### ###### ##### ##### ###### #0 ##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 436</t>
   </si>
   <si>
-    <t>##### #### ##### ##### ##### ######## ###### #0 ##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 437</t>
   </si>
   <si>
-    <t>##### #### ##### ##### ##### ######## ####### #0 ##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 438</t>
   </si>
   <si>
-    <t>####### ###### ##### ####### ### #0 ##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 439</t>
   </si>
   <si>
-    <t>####### ###### ###### ###### ###### ######## #0 ##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 440</t>
   </si>
   <si>
-    <t>##### ###### ######### ### ######### ### ###### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##### ###### ######### ##### ######### ### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##### ###### ######### ### ######### ### ####### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####### ##### ##### ##### ######### ### ###### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####### ##### ##### ##### ######### ### ####### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ##### #### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>###### #### ##### ######### #### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>###### #### ##### ######### #### #0 ##y #</t>
-  </si>
-  <si>
-    <t>#### ##### ###### ##### ######### ##### ##### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>###### #### ###### ##### ##### ###### ###### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>###### #### ###### ##### ##### ###### ####### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>###### ### ### ######### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>######## ####### ######## #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####### ###### ###### ######### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##### ####### ######## #0 ##0 #</t>
-  </si>
-  <si>
-    <t>### ##### ######## #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######## #0 ##0 #</t>
-  </si>
-  <si>
-    <t>#### ####### #### ####### ##### ###### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##### ######### ##### #### ### ######## ###### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##### ######### ##### #### ### ######## ####### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##### ######### ##### #### ### ######## ####### #0 ###0#</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######### ###### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>#0 ##0 ########## ##### ###### ### ###### #0 ##0 1</t>
-  </si>
-  <si>
-    <t>#0 ##0 ########## ##### ###### ### ###### #0 ##0 2</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######### ###### #0 #0 #</t>
-  </si>
-  <si>
-    <t>#0 ##0 ########## ##### ###### ### ###### #0 ##0 3</t>
-  </si>
-  <si>
-    <t>#0 ##0 ########## ##### ###### ### ###### #0 ##0 4</t>
-  </si>
-  <si>
-    <t>###### ####0 ###### ###### ###### ### ###### #### ##### ###### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>###### ####0 ###### ###### ###### ### ###### #### ##### ###### #0 ##0 5</t>
-  </si>
-  <si>
-    <t>###### ####0 ###### ###### ###### ### ###### #### ##### ####### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>### ######### #### ##### #### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>### ######### #### ##### #### ####### ##### ## #####</t>
-  </si>
-  <si>
-    <t>### ######### #### ##### #### ###### ##### ## #####</t>
-  </si>
-  <si>
-    <t>######## ####### #### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>######## ####### #### ####### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>#### ##### ##### #### ###### #0##0 #</t>
-  </si>
-  <si>
-    <t>##### ##### ###### ##### ########## #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##### ######## ##### ####### ######### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##### ######## ##### ####### ######### #0 ## #</t>
-  </si>
-  <si>
-    <t>##### #### ########### ####### ###### ######## ##### ####### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>###### ### ##### ##### ####### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>######## ######## #### ##### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##### ##### ###### ######### ##### ####### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##0 ####### ##### ##### ##### ####### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>###### #### ##0##0##### ######### ######## ##### #0##0 #</t>
-  </si>
-  <si>
-    <t>###### #### ##0##0##### ######### ######## ##### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######## ##### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##### ##### ##0##0 #####e ######## ##### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### ##### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>######### ######## ########## ##### ### ##0 # ######## #0 ##0 #</t>
-  </si>
-  <si>
-    <t>#### ##0##0 ##### ##### ###### ######## #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ######### ####### ######## #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##### ####### #### ######### ####### ######## #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##0##0 #### ##### ##### ######## #### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##0##0 #### ##### ##### ######## #### #0##0 #</t>
-  </si>
-  <si>
-    <t>###### #### ##0##0 ##### #### ##### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>######### ######## ##### ##0##0##0##0 #0 ##0 #</t>
-  </si>
-  <si>
-    <t>######### ######## ##### ##0##0##0##0 #0 ##y #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ##### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0 ###### ##### ##### ##### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0 ###### ##### ##### ##### #0 #0 #</t>
-  </si>
-  <si>
-    <t>##### ###### ######### ###### ###### ##### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>#### ######## ##### ############ #0##0 #</t>
-  </si>
-  <si>
-    <t>#### ######## ##### ############ #0 ##0 #</t>
-  </si>
-  <si>
-    <t>######## ###### ##### ############ #0##0#</t>
-  </si>
-  <si>
-    <t>######## ###### ##### ############ #0 ##0#</t>
-  </si>
-  <si>
-    <t>######## ###### ##### ############ #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0 ##0 ###### ####### #0 ##0#</t>
-  </si>
-  <si>
-    <t>##0 ##0 ######## ##### ######## ### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##### ### ### ###### ####### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##### ### ### ###### ####### #0##0 #</t>
-  </si>
-  <si>
-    <t>##### ##0 ##0 ##0 ###### ####### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ####### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### ######### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #### ######## #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ######## #### ##### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ##### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##0 ##0 ##### ######## #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######## #0 ###0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ###### ####### ##### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ###### ###### ##### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ####### #0##0 #</t>
-  </si>
-  <si>
-    <t>##0##0 ### ##### ##### ####### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##### ####### ####### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>### ######## ####### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ######### ######### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##### #### ######### ##### #### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ########### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>####0 ##0 ########### #0##0 #</t>
-  </si>
-  <si>
-    <t>####### ##### ##### ###### ######## #0 ##0 #</t>
-  </si>
-  <si>
-    <t>##### ##### #### ##### ##### ###### ######## #0 ##0 #</t>
-  </si>
-  <si>
-    <t>### ####0 ##0 ##0 ##### ######### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>### ####0 ##0 ##0 ##### ######### #0 ##0#</t>
-  </si>
-  <si>
-    <t>### ####0 ##0 ##0 ##### ######### #0##0 #</t>
-  </si>
-  <si>
-    <t>###### #### ##0##0 ##### #0 ##0 #</t>
-  </si>
-  <si>
-    <t>#### ##### ## ###### ##### ####### #### #### #0 ##0 #</t>
+    <t>NAN ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 441</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -506,8 +281,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -523,7 +306,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -531,12 +314,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -835,85 +636,157 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>139</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>141</v>
+        <v>66</v>
       </c>
       <c r="F2" t="s">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="G2" t="s">
-        <v>143</v>
+        <v>68</v>
       </c>
       <c r="H2" t="s">
-        <v>144</v>
+        <v>69</v>
       </c>
       <c r="I2" t="s">
-        <v>145</v>
+        <v>70</v>
       </c>
       <c r="J2" t="s">
-        <v>146</v>
+        <v>71</v>
       </c>
       <c r="K2" t="s">
-        <v>147</v>
+        <v>72</v>
       </c>
       <c r="L2" t="s">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="M2" t="s">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="N2" t="s">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="O2" t="s">
-        <v>151</v>
+        <v>76</v>
       </c>
       <c r="P2" t="s">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="Q2" t="s">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="R2" t="s">
-        <v>154</v>
+        <v>79</v>
       </c>
       <c r="S2" t="s">
-        <v>155</v>
+        <v>80</v>
       </c>
       <c r="T2" t="s">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="U2" t="s">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="V2" t="s">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="W2" t="s">
-        <v>159</v>
+        <v>84</v>
       </c>
       <c r="X2" t="s">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="Y2" t="s">
-        <v>161</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -921,7 +794,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <v>1192</v>
@@ -998,7 +871,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>1183</v>
@@ -1075,7 +948,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>1178</v>
@@ -1152,7 +1025,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>1165</v>
@@ -1229,7 +1102,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>1164</v>
@@ -1306,7 +1179,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C8">
         <v>1257</v>
@@ -1383,7 +1256,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C9">
         <v>923</v>
@@ -1460,7 +1333,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C10">
         <v>935</v>
@@ -1537,7 +1410,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C11">
         <v>737</v>
@@ -1614,7 +1487,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C12">
         <v>985</v>
@@ -1691,7 +1564,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C13">
         <v>829</v>
@@ -1768,7 +1641,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C14">
         <v>1072</v>
@@ -1845,7 +1718,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C15">
         <v>1181</v>
@@ -1922,7 +1795,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C16">
         <v>1192</v>
@@ -1999,7 +1872,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C17">
         <v>1154</v>
@@ -2076,7 +1949,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C18">
         <v>963</v>
@@ -2153,7 +2026,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="C19">
         <v>1165</v>
@@ -2230,7 +2103,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="C20">
         <v>1028</v>
@@ -2307,7 +2180,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="C21">
         <v>834</v>
@@ -2384,7 +2257,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="C22">
         <v>829</v>
@@ -2461,7 +2334,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C23">
         <v>1132</v>
@@ -2538,7 +2411,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C24">
         <v>1166</v>
@@ -2615,7 +2488,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C25">
         <v>1184</v>
@@ -2692,7 +2565,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C26">
         <v>1073</v>
@@ -2769,7 +2642,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C27">
         <v>1172</v>
@@ -2846,7 +2719,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C28">
         <v>1025</v>
@@ -2923,7 +2796,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C29">
         <v>852</v>
@@ -3000,7 +2873,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C30">
         <v>943</v>
@@ -3077,7 +2950,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C31">
         <v>1122</v>
@@ -3154,7 +3027,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C32">
         <v>1095</v>
@@ -3231,7 +3104,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C33">
         <v>1188</v>
@@ -3308,7 +3181,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C34">
         <v>756</v>
@@ -3385,7 +3258,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C35">
         <v>1095</v>
@@ -3462,7 +3335,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C36">
         <v>757</v>
@@ -3539,7 +3412,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C37">
         <v>881</v>
@@ -3616,7 +3489,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C38">
         <v>1186</v>
@@ -3693,7 +3566,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C39">
         <v>1013</v>
@@ -3770,7 +3643,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C40">
         <v>1186</v>
@@ -3847,7 +3720,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C41">
         <v>1090</v>
@@ -3924,7 +3797,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C42">
         <v>1246</v>
@@ -4001,7 +3874,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C43">
         <v>1071</v>
@@ -4078,7 +3951,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C44">
         <v>1032</v>
@@ -4155,7 +4028,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C45">
         <v>1062</v>
@@ -4232,7 +4105,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C46">
         <v>1141</v>
@@ -4309,7 +4182,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C47">
         <v>954</v>
@@ -4386,7 +4259,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C48">
         <v>920</v>
@@ -4463,7 +4336,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C49">
         <v>1155</v>
@@ -4540,7 +4413,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C50">
         <v>963</v>
@@ -4617,7 +4490,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C51">
         <v>873</v>
@@ -4694,7 +4567,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C52">
         <v>1147</v>
@@ -4771,7 +4644,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C53">
         <v>849</v>
@@ -4848,7 +4721,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C54">
         <v>816</v>
@@ -4925,7 +4798,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C55">
         <v>1183</v>
@@ -5002,7 +4875,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C56">
         <v>1170</v>
@@ -5079,7 +4952,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C57">
         <v>850</v>
@@ -5156,7 +5029,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C58">
         <v>1134</v>
@@ -5233,7 +5106,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C59">
         <v>1098</v>
@@ -5310,7 +5183,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C60">
         <v>1181</v>
@@ -5387,7 +5260,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C61">
         <v>1076</v>
@@ -5464,7 +5337,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C62">
         <v>824</v>
@@ -5541,7 +5414,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C63">
         <v>987</v>
@@ -5618,7 +5491,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C64">
         <v>902</v>
@@ -5695,7 +5568,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C65">
         <v>1158</v>
@@ -5772,7 +5645,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C66">
         <v>1122</v>
@@ -5849,7 +5722,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C67">
         <v>1127</v>
@@ -5926,7 +5799,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C68">
         <v>786</v>
@@ -6003,7 +5876,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C69">
         <v>811</v>
@@ -6080,7 +5953,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C70">
         <v>1080</v>
@@ -6157,7 +6030,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C71">
         <v>1077</v>
@@ -6234,7 +6107,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C72">
         <v>811</v>
@@ -6311,7 +6184,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C73">
         <v>790</v>
@@ -6388,7 +6261,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C74">
         <v>748</v>
@@ -6465,7 +6338,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C75">
         <v>802</v>
@@ -6542,7 +6415,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C76">
         <v>812</v>
@@ -6619,7 +6492,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C77">
         <v>887</v>
@@ -6696,7 +6569,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C78">
         <v>850</v>
@@ -6773,7 +6646,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C79">
         <v>942</v>
@@ -6850,7 +6723,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C80">
         <v>1134</v>
@@ -6927,7 +6800,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C81">
         <v>1090</v>
@@ -7158,7 +7031,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C84">
         <v>1141</v>
@@ -7235,7 +7108,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C85">
         <v>1146</v>
@@ -7312,7 +7185,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C86">
         <v>662</v>
@@ -7389,7 +7262,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C87">
         <v>1118</v>
@@ -7466,7 +7339,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C88">
         <v>1183</v>
@@ -7543,7 +7416,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C89">
         <v>1095</v>
@@ -7620,7 +7493,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C90">
         <v>1065</v>
@@ -7697,7 +7570,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C91">
         <v>1134</v>
@@ -7774,7 +7647,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C92">
         <v>1121</v>
@@ -8005,7 +7878,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C95">
         <v>1017</v>
@@ -8082,7 +7955,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C96">
         <v>1040</v>
@@ -8159,7 +8032,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C97">
         <v>1092</v>
@@ -8236,7 +8109,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C98">
         <v>1098</v>
@@ -8313,7 +8186,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C99">
         <v>1008</v>
@@ -8390,7 +8263,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C100">
         <v>829</v>
@@ -8467,7 +8340,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C101">
         <v>1159</v>
@@ -8544,7 +8417,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C102">
         <v>1030</v>
@@ -8621,7 +8494,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C103">
         <v>730</v>
@@ -8698,7 +8571,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C104">
         <v>968</v>
@@ -8775,7 +8648,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C105">
         <v>961</v>
@@ -8852,7 +8725,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C106">
         <v>891</v>
@@ -8929,7 +8802,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C107">
         <v>1093</v>
@@ -9006,7 +8879,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C108">
         <v>1009</v>
@@ -9083,7 +8956,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C109">
         <v>1191</v>
@@ -9160,7 +9033,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C110">
         <v>1194</v>
@@ -9237,7 +9110,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C111">
         <v>1164</v>
@@ -9314,7 +9187,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C112">
         <v>1065</v>
@@ -9391,7 +9264,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C113">
         <v>1009</v>
@@ -9468,7 +9341,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C114">
         <v>715</v>
@@ -9545,7 +9418,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C115">
         <v>984</v>
@@ -9622,7 +9495,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C116">
         <v>1166</v>
@@ -9699,7 +9572,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C117">
         <v>1104</v>
@@ -9776,7 +9649,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C118">
         <v>1056</v>
@@ -9853,7 +9726,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C119">
         <v>655</v>
@@ -9930,7 +9803,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C120">
         <v>1029</v>
@@ -10007,7 +9880,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C121">
         <v>1010</v>
@@ -10084,7 +9957,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C122">
         <v>850</v>
@@ -10161,7 +10034,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C123">
         <v>1160</v>
@@ -10238,7 +10111,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C124">
         <v>1201</v>
@@ -10315,7 +10188,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C125">
         <v>1194</v>
@@ -10392,7 +10265,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C126">
         <v>1110</v>
@@ -10469,7 +10342,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C127">
         <v>1038</v>
@@ -10546,7 +10419,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C128">
         <v>1069</v>
@@ -10623,7 +10496,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C129">
         <v>1145</v>
@@ -10700,7 +10573,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C130">
         <v>849</v>
@@ -10777,7 +10650,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C131">
         <v>893</v>
@@ -10854,7 +10727,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C132">
         <v>1050</v>
@@ -10931,7 +10804,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C133">
         <v>945</v>
@@ -11008,7 +10881,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C134">
         <v>1026</v>
@@ -11085,7 +10958,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C135">
         <v>887</v>
@@ -11162,7 +11035,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C136">
         <v>790</v>
@@ -11239,7 +11112,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C137">
         <v>1161</v>
@@ -11316,7 +11189,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C138">
         <v>1186</v>
@@ -11393,7 +11266,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C139">
         <v>1166</v>
@@ -11470,7 +11343,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C140">
         <v>1140</v>
@@ -11547,7 +11420,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C141">
         <v>1182</v>
@@ -11624,7 +11497,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C142">
         <v>1165</v>
@@ -11701,7 +11574,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C143">
         <v>1200</v>
@@ -11778,7 +11651,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C144">
         <v>1116</v>
@@ -11855,7 +11728,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C145">
         <v>1083</v>
@@ -11932,7 +11805,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C146">
         <v>993</v>
@@ -12009,7 +11882,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C147">
         <v>868</v>
@@ -12086,7 +11959,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C148">
         <v>782</v>
@@ -12163,7 +12036,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C149">
         <v>1172</v>
@@ -12240,7 +12113,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C150">
         <v>690</v>
@@ -12317,7 +12190,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C151">
         <v>890</v>
@@ -12394,7 +12267,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C152">
         <v>926</v>
@@ -12471,7 +12344,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C153">
         <v>1166</v>
@@ -12548,7 +12421,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C154">
         <v>1148</v>
@@ -12625,7 +12498,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C155">
         <v>961</v>
@@ -12702,7 +12575,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C156">
         <v>996</v>
@@ -12779,7 +12652,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C157">
         <v>770</v>
@@ -12856,7 +12729,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C158">
         <v>987</v>
@@ -12933,7 +12806,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C159">
         <v>1079</v>
@@ -13010,7 +12883,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C160">
         <v>1030</v>
@@ -13087,7 +12960,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C161">
         <v>1193</v>
@@ -13164,7 +13037,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C162">
         <v>1180</v>
@@ -13241,7 +13114,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C163">
         <v>1226</v>
@@ -13318,7 +13191,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C164">
         <v>1124</v>
@@ -13395,7 +13268,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C165">
         <v>1088</v>
@@ -13472,7 +13345,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C166">
         <v>1159</v>
@@ -13549,7 +13422,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C167">
         <v>915</v>
@@ -13626,7 +13499,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C168">
         <v>895</v>
@@ -13703,7 +13576,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C169">
         <v>814</v>
@@ -13780,7 +13653,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C170">
         <v>575</v>
@@ -13857,7 +13730,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C171">
         <v>1040</v>
@@ -13934,7 +13807,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C172">
         <v>873</v>
@@ -14011,7 +13884,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C173">
         <v>925</v>
@@ -14088,7 +13961,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C174">
         <v>781</v>
@@ -14165,7 +14038,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C175">
         <v>935</v>
@@ -14242,7 +14115,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C176">
         <v>1099</v>
@@ -14319,7 +14192,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C177">
         <v>1103</v>
@@ -14396,7 +14269,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C178">
         <v>1101</v>
@@ -14473,7 +14346,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C179">
         <v>1017</v>
@@ -14550,7 +14423,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C180">
         <v>760</v>
@@ -14627,7 +14500,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C181">
         <v>1133</v>
@@ -14704,7 +14577,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C182">
         <v>856</v>
@@ -14781,7 +14654,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C183">
         <v>852</v>
@@ -14858,7 +14731,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="C184">
         <v>828</v>
@@ -14935,7 +14808,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="C185">
         <v>822</v>
@@ -15012,7 +14885,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="C186">
         <v>1173</v>
@@ -15089,7 +14962,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="C187">
         <v>1125</v>
@@ -15166,7 +15039,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="C188">
         <v>867</v>
@@ -15243,7 +15116,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="C189">
         <v>896</v>
@@ -15320,7 +15193,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="C190">
         <v>1028</v>
@@ -15397,7 +15270,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="C191">
         <v>1110</v>
@@ -15474,7 +15347,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="C192">
         <v>1158</v>
@@ -15551,7 +15424,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="C193">
         <v>1085</v>
@@ -15628,7 +15501,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="C194">
         <v>1155</v>
@@ -15705,7 +15578,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C195">
         <v>1042</v>
@@ -15782,7 +15655,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="C196">
         <v>1053</v>
@@ -15859,7 +15732,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C197">
         <v>1081</v>
@@ -15936,7 +15809,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C198">
         <v>1110</v>
@@ -16013,7 +15886,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C199">
         <v>835</v>
@@ -16090,7 +15963,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C200">
         <v>1224</v>
@@ -16167,7 +16040,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C201">
         <v>1139</v>
@@ -16244,7 +16117,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C202">
         <v>1190</v>
@@ -16321,7 +16194,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C203">
         <v>1141</v>
@@ -16398,7 +16271,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C204">
         <v>1171</v>
@@ -16475,7 +16348,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C205">
         <v>1080</v>
@@ -16552,7 +16425,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C206">
         <v>1124</v>
@@ -16629,7 +16502,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C207">
         <v>1069</v>
@@ -16706,7 +16579,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C208">
         <v>1150</v>
@@ -16783,7 +16656,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="C209">
         <v>915</v>
@@ -16860,7 +16733,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="C210">
         <v>769</v>
@@ -16937,7 +16810,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="C211">
         <v>1112</v>
@@ -17014,7 +16887,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="C212">
         <v>1087</v>
@@ -17091,7 +16964,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="C213">
         <v>932</v>
@@ -17168,7 +17041,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="C214">
         <v>997</v>
@@ -17245,7 +17118,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="C215">
         <v>1147</v>
@@ -17322,7 +17195,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="C216">
         <v>1194</v>
@@ -17399,7 +17272,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="C217">
         <v>1046</v>
@@ -17476,7 +17349,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="C218">
         <v>1065</v>
@@ -17553,7 +17426,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="C219">
         <v>1194</v>
@@ -17630,7 +17503,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="C220">
         <v>1038</v>
@@ -17707,7 +17580,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="C221">
         <v>746</v>
@@ -17784,7 +17657,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C222">
         <v>1156</v>
@@ -17861,7 +17734,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C223">
         <v>1091</v>
@@ -17938,7 +17811,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C224">
         <v>1011</v>
@@ -18015,7 +17888,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="C225">
         <v>990</v>
@@ -18092,7 +17965,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C226">
         <v>969</v>
@@ -18169,7 +18042,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="C227">
         <v>1030</v>
@@ -18246,7 +18119,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="C228">
         <v>1116</v>
@@ -18323,7 +18196,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="C229">
         <v>1075</v>
@@ -18400,7 +18273,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="C230">
         <v>1072</v>
@@ -18477,7 +18350,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="C231">
         <v>1136</v>
@@ -18554,7 +18427,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="C232">
         <v>973</v>
@@ -18631,7 +18504,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="C233">
         <v>915</v>
@@ -18708,7 +18581,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="C234">
         <v>977</v>
@@ -18785,7 +18658,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="C235">
         <v>876</v>
@@ -18862,7 +18735,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="C236">
         <v>1168</v>
@@ -18939,7 +18812,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="C237">
         <v>1056</v>
@@ -19016,7 +18889,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="C238">
         <v>1082</v>
@@ -19093,7 +18966,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="C239">
         <v>976</v>
@@ -19170,7 +19043,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="C240">
         <v>941</v>
@@ -19247,7 +19120,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="C241">
         <v>893</v>
@@ -19324,7 +19197,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="C242">
         <v>892</v>
@@ -19401,7 +19274,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="C243">
         <v>1038</v>
@@ -19478,7 +19351,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="C244">
         <v>1133</v>
@@ -19555,7 +19428,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="C245">
         <v>1075</v>
@@ -19632,7 +19505,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="C246">
         <v>1153</v>
@@ -19709,7 +19582,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C247">
         <v>1189</v>
@@ -19786,7 +19659,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="C248">
         <v>1238</v>
@@ -19863,7 +19736,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C249">
         <v>1163</v>
@@ -19940,7 +19813,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C250">
         <v>1164</v>
@@ -20017,7 +19890,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="C251">
         <v>1048</v>
@@ -20094,7 +19967,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="C252">
         <v>1140</v>
@@ -20171,7 +20044,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="C253">
         <v>541</v>
@@ -20248,7 +20121,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="C254">
         <v>1144</v>
@@ -20325,7 +20198,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="C255">
         <v>1156</v>
@@ -20402,7 +20275,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="C256">
         <v>1000</v>
@@ -20479,7 +20352,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="C257">
         <v>1170</v>
@@ -20556,7 +20429,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="C258">
         <v>1051</v>
@@ -20633,7 +20506,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="C259">
         <v>1021</v>
@@ -20710,7 +20583,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="C260">
         <v>1155</v>
@@ -20787,7 +20660,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="C261">
         <v>1184</v>
@@ -20864,7 +20737,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="C262">
         <v>1156</v>
@@ -20941,7 +20814,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="C263">
         <v>1145</v>
@@ -21018,7 +20891,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="C264">
         <v>1140</v>
@@ -21095,7 +20968,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="C265">
         <v>968</v>
@@ -21172,7 +21045,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="C266">
         <v>857</v>
@@ -21249,7 +21122,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="C267">
         <v>1003</v>
@@ -21326,7 +21199,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="C268">
         <v>902</v>
@@ -21403,7 +21276,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="C269">
         <v>976</v>
@@ -21480,7 +21353,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="C270">
         <v>1134</v>
@@ -21557,7 +21430,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="C271">
         <v>1113</v>
@@ -21634,7 +21507,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="C272">
         <v>1183</v>
@@ -21711,7 +21584,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="C273">
         <v>1057</v>
@@ -21788,7 +21661,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="C274">
         <v>1025</v>
@@ -21865,7 +21738,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="C275">
         <v>728</v>
@@ -21942,7 +21815,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="C276">
         <v>1133</v>
@@ -22019,7 +21892,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="C277">
         <v>935</v>
@@ -22096,7 +21969,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="C278">
         <v>1180</v>
@@ -22173,7 +22046,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="C279">
         <v>1128</v>
@@ -22250,7 +22123,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="C280">
         <v>1237</v>
@@ -22327,7 +22200,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="C281">
         <v>1223</v>
@@ -22404,7 +22277,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="C282">
         <v>1105</v>
@@ -22481,7 +22354,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="C283">
         <v>1015</v>
@@ -22558,7 +22431,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="C284">
         <v>1213</v>
@@ -22635,7 +22508,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="C285">
         <v>1176</v>
@@ -22712,7 +22585,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="C286">
         <v>945</v>
@@ -22789,7 +22662,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="C287">
         <v>1030</v>
@@ -22866,7 +22739,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="C288">
         <v>992</v>
@@ -22943,7 +22816,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="C289">
         <v>963</v>
@@ -23020,7 +22893,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="C290">
         <v>880</v>
@@ -23097,7 +22970,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="C291">
         <v>571</v>
@@ -23174,7 +23047,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="C292">
         <v>831</v>
@@ -23251,7 +23124,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="C293">
         <v>1137</v>
@@ -23328,7 +23201,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="C294">
         <v>1147</v>
@@ -23405,7 +23278,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="C295">
         <v>1059</v>
@@ -23482,7 +23355,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="C296">
         <v>1125</v>
@@ -23559,7 +23432,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="C297">
         <v>916</v>
@@ -23636,7 +23509,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="C298">
         <v>947</v>
@@ -23713,7 +23586,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="C299">
         <v>719</v>
@@ -23790,7 +23663,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="C300">
         <v>990</v>
@@ -23867,7 +23740,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="C301">
         <v>1059</v>
@@ -23944,7 +23817,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="C302">
         <v>1006</v>
@@ -24021,7 +23894,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="C303">
         <v>878</v>
@@ -24098,7 +23971,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="C304">
         <v>1187</v>
@@ -24175,7 +24048,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="C305">
         <v>1243</v>
@@ -24252,7 +24125,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="C306">
         <v>1169</v>
@@ -24329,7 +24202,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="C307">
         <v>1009</v>
@@ -24406,7 +24279,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="C308">
         <v>1108</v>
@@ -24483,7 +24356,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="C309">
         <v>1079</v>
@@ -24560,7 +24433,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="C310">
         <v>1083</v>
@@ -24637,7 +24510,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="C311">
         <v>1068</v>
@@ -24714,7 +24587,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="C312">
         <v>640</v>
@@ -24791,7 +24664,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="C313">
         <v>960</v>
@@ -24868,7 +24741,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="C314">
         <v>851</v>
@@ -24945,7 +24818,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="C315">
         <v>1093</v>
@@ -25022,7 +24895,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="C316">
         <v>1190</v>
@@ -25099,7 +24972,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="C317">
         <v>1152</v>
@@ -25176,7 +25049,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="C318">
         <v>1095</v>
@@ -25253,7 +25126,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="C319">
         <v>1177</v>
@@ -25330,7 +25203,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="C320">
         <v>706</v>
@@ -25407,7 +25280,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="C321">
         <v>1110</v>
@@ -25484,7 +25357,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="C322">
         <v>1137</v>
@@ -25561,7 +25434,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="C323">
         <v>1162</v>
@@ -25638,7 +25511,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="C324">
         <v>821</v>
@@ -25715,7 +25588,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>95</v>
+        <v>27</v>
       </c>
       <c r="C325">
         <v>808</v>
@@ -25792,7 +25665,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="C326">
         <v>1121</v>
@@ -25869,7 +25742,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="C327">
         <v>1202</v>
@@ -25946,7 +25819,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="C328">
         <v>1187</v>
@@ -26023,7 +25896,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="C329">
         <v>911</v>
@@ -26100,7 +25973,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="C330">
         <v>1176</v>
@@ -26177,7 +26050,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="C331">
         <v>1060</v>
@@ -26254,7 +26127,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="C332">
         <v>1022</v>
@@ -26331,7 +26204,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="C333">
         <v>1231</v>
@@ -26408,7 +26281,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="C334">
         <v>1197</v>
@@ -26485,7 +26358,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="C335">
         <v>1111</v>
@@ -26562,7 +26435,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="C336">
         <v>998</v>
@@ -26639,7 +26512,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="C337">
         <v>1017</v>
@@ -26716,7 +26589,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="C338">
         <v>1050</v>
@@ -26793,7 +26666,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="C339">
         <v>1151</v>
@@ -26870,7 +26743,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="C340">
         <v>963</v>
@@ -26947,7 +26820,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="C341">
         <v>1121</v>
@@ -27024,7 +26897,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="C342">
         <v>838</v>
@@ -27101,7 +26974,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="C343">
         <v>635</v>
@@ -27178,7 +27051,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="C344">
         <v>1203</v>
@@ -27255,7 +27128,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>106</v>
+        <v>27</v>
       </c>
       <c r="C345">
         <v>720</v>
@@ -27332,7 +27205,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="C346">
         <v>1249</v>
@@ -27409,7 +27282,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="C347">
         <v>1116</v>
@@ -27486,7 +27359,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="C348">
         <v>1169</v>
@@ -27563,7 +27436,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="C349">
         <v>712</v>
@@ -27640,7 +27513,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C350">
         <v>1219</v>
@@ -27717,7 +27590,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="C351">
         <v>582</v>
@@ -27794,7 +27667,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="C352">
         <v>1172</v>
@@ -27871,7 +27744,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="C353">
         <v>1199</v>
@@ -27948,7 +27821,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="C354">
         <v>1198</v>
@@ -28025,7 +27898,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C355">
         <v>1074</v>
@@ -28102,7 +27975,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="C356">
         <v>824</v>
@@ -28179,7 +28052,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="C357">
         <v>899</v>
@@ -28256,7 +28129,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="C358">
         <v>1146</v>
@@ -28333,7 +28206,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="C359">
         <v>1028</v>
@@ -28410,7 +28283,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="C360">
         <v>866</v>
@@ -28487,7 +28360,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="C361">
         <v>958</v>
@@ -28564,7 +28437,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="C362">
         <v>868</v>
@@ -28641,7 +28514,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="C363">
         <v>701</v>
@@ -28718,7 +28591,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="C364">
         <v>1009</v>
@@ -28795,7 +28668,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="C365">
         <v>1065</v>
@@ -28872,7 +28745,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>116</v>
+        <v>27</v>
       </c>
       <c r="C366">
         <v>674</v>
@@ -28949,7 +28822,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>117</v>
+        <v>27</v>
       </c>
       <c r="C367">
         <v>1157</v>
@@ -29026,7 +28899,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>117</v>
+        <v>27</v>
       </c>
       <c r="C368">
         <v>1075</v>
@@ -29103,7 +28976,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>118</v>
+        <v>27</v>
       </c>
       <c r="C369">
         <v>1110</v>
@@ -29180,7 +29053,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>118</v>
+        <v>27</v>
       </c>
       <c r="C370">
         <v>899</v>
@@ -29257,7 +29130,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>118</v>
+        <v>27</v>
       </c>
       <c r="C371">
         <v>1155</v>
@@ -29334,7 +29207,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="C372">
         <v>1196</v>
@@ -29411,7 +29284,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="C373">
         <v>1185</v>
@@ -29488,7 +29361,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="C374">
         <v>1140</v>
@@ -29565,7 +29438,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="C375">
         <v>1116</v>
@@ -29642,7 +29515,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="C376">
         <v>783</v>
@@ -29719,7 +29592,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="C377">
         <v>602</v>
@@ -29796,7 +29669,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="C378">
         <v>1234</v>
@@ -29873,7 +29746,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="C379">
         <v>1199</v>
@@ -29950,7 +29823,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="C380">
         <v>697</v>
@@ -30027,7 +29900,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="C381">
         <v>610</v>
@@ -30104,7 +29977,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="C382">
         <v>993</v>
@@ -30181,7 +30054,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="C383">
         <v>1109</v>
@@ -30258,7 +30131,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="C384">
         <v>881</v>
@@ -30335,7 +30208,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="C385">
         <v>900</v>
@@ -30412,7 +30285,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="C386">
         <v>1123</v>
@@ -30489,7 +30362,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="C387">
         <v>900</v>
@@ -30566,7 +30439,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="C388">
         <v>1151</v>
@@ -30643,7 +30516,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>123</v>
+        <v>27</v>
       </c>
       <c r="C389">
         <v>1188</v>
@@ -30720,7 +30593,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>123</v>
+        <v>27</v>
       </c>
       <c r="C390">
         <v>1161</v>
@@ -30797,7 +30670,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>123</v>
+        <v>27</v>
       </c>
       <c r="C391">
         <v>917</v>
@@ -30874,7 +30747,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>123</v>
+        <v>27</v>
       </c>
       <c r="C392">
         <v>1004</v>
@@ -30951,7 +30824,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>123</v>
+        <v>27</v>
       </c>
       <c r="C393">
         <v>638</v>
@@ -31028,7 +30901,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>123</v>
+        <v>27</v>
       </c>
       <c r="C394">
         <v>981</v>
@@ -31105,7 +30978,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="C395">
         <v>977</v>
@@ -31182,7 +31055,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>124</v>
+        <v>27</v>
       </c>
       <c r="C396">
         <v>943</v>
@@ -31259,7 +31132,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="C397">
         <v>1170</v>
@@ -31336,7 +31209,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="C398">
         <v>1062</v>
@@ -31413,7 +31286,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="C399">
         <v>1031</v>
@@ -31490,7 +31363,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="C400">
         <v>1139</v>
@@ -31567,7 +31440,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="C401">
         <v>1153</v>
@@ -31644,7 +31517,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="C402">
         <v>1152</v>
@@ -31721,7 +31594,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="C403">
         <v>1096</v>
@@ -31798,7 +31671,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="C404">
         <v>1061</v>
@@ -31875,7 +31748,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="C405">
         <v>1075</v>
@@ -31952,7 +31825,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="C406">
         <v>970</v>
@@ -32029,7 +31902,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>127</v>
+        <v>27</v>
       </c>
       <c r="C407">
         <v>1109</v>
@@ -32106,7 +31979,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>127</v>
+        <v>27</v>
       </c>
       <c r="C408">
         <v>948</v>
@@ -32183,7 +32056,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="C409">
         <v>461</v>
@@ -32260,7 +32133,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>128</v>
+        <v>30</v>
       </c>
       <c r="C410">
         <v>1139</v>
@@ -32337,7 +32210,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>128</v>
+        <v>31</v>
       </c>
       <c r="C411">
         <v>782</v>
@@ -32414,7 +32287,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C412">
         <v>1112</v>
@@ -32491,7 +32364,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="C413">
         <v>1040</v>
@@ -32568,7 +32441,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>129</v>
+        <v>34</v>
       </c>
       <c r="C414">
         <v>968</v>
@@ -32645,7 +32518,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>129</v>
+        <v>35</v>
       </c>
       <c r="C415">
         <v>815</v>
@@ -32722,7 +32595,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>129</v>
+        <v>36</v>
       </c>
       <c r="C416">
         <v>1087</v>
@@ -32799,7 +32672,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>129</v>
+        <v>37</v>
       </c>
       <c r="C417">
         <v>803</v>
@@ -32876,7 +32749,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>130</v>
+        <v>38</v>
       </c>
       <c r="C418">
         <v>970</v>
@@ -32953,7 +32826,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>130</v>
+        <v>39</v>
       </c>
       <c r="C419">
         <v>887</v>
@@ -33030,7 +32903,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="C420">
         <v>862</v>
@@ -33107,7 +32980,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="C421">
         <v>890</v>
@@ -33184,7 +33057,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>132</v>
+        <v>42</v>
       </c>
       <c r="C422">
         <v>1155</v>
@@ -33261,7 +33134,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="C423">
         <v>1137</v>
@@ -33338,7 +33211,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>132</v>
+        <v>44</v>
       </c>
       <c r="C424">
         <v>1224</v>
@@ -33415,7 +33288,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>132</v>
+        <v>45</v>
       </c>
       <c r="C425">
         <v>1141</v>
@@ -33492,7 +33365,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>133</v>
+        <v>46</v>
       </c>
       <c r="C426">
         <v>1159</v>
@@ -33569,7 +33442,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>133</v>
+        <v>47</v>
       </c>
       <c r="C427">
         <v>1058</v>
@@ -33646,7 +33519,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>133</v>
+        <v>48</v>
       </c>
       <c r="C428">
         <v>970</v>
@@ -33723,7 +33596,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="C429">
         <v>1125</v>
@@ -33800,7 +33673,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>133</v>
+        <v>50</v>
       </c>
       <c r="C430">
         <v>1158</v>
@@ -33877,7 +33750,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>133</v>
+        <v>51</v>
       </c>
       <c r="C431">
         <v>1003</v>
@@ -33954,7 +33827,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="C432">
         <v>880</v>
@@ -34031,7 +33904,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>134</v>
+        <v>53</v>
       </c>
       <c r="C433">
         <v>1105</v>
@@ -34108,7 +33981,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>135</v>
+        <v>54</v>
       </c>
       <c r="C434">
         <v>1182</v>
@@ -34185,7 +34058,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="C435">
         <v>1193</v>
@@ -34262,7 +34135,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="C436">
         <v>974</v>
@@ -34339,7 +34212,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="C437">
         <v>1156</v>
@@ -34416,7 +34289,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>137</v>
+        <v>58</v>
       </c>
       <c r="C438">
         <v>1076</v>
@@ -34493,7 +34366,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>137</v>
+        <v>59</v>
       </c>
       <c r="C439">
         <v>1120</v>
@@ -34570,7 +34443,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="C440">
         <v>843</v>
@@ -34647,7 +34520,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>138</v>
+        <v>61</v>
       </c>
       <c r="C441">
         <v>868</v>
@@ -34724,7 +34597,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>138</v>
+        <v>62</v>
       </c>
       <c r="C442">
         <v>1142</v>
@@ -34801,7 +34674,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>138</v>
+        <v>63</v>
       </c>
       <c r="C443">
         <v>992</v>
